--- a/deliverables/风险实证图解/风险实证记录表.xlsx
+++ b/deliverables/风险实证图解/风险实证记录表.xlsx
@@ -960,7 +960,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>生成时间：2026-10-11T00:33:30+08:00　　数据来源：离线复现（内置模型）</t>
+          <t>生成时间：2026-10-12T19:43:49+08:00　　数据来源：离线复现（内置模型）</t>
         </is>
       </c>
     </row>
